--- a/data/shopping.xlsx
+++ b/data/shopping.xlsx
@@ -7125,32 +7125,32 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Water heater 50 L</t>
+          <t>Water heater, flat 60 L, horizontal mounting</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Ariston Velis Pro 50 EU NEW (Technomarket 09242822)</t>
+          <t>Eldom Galant DU060W (60 L, 2.1+1.2 kW, universal mounting, el. control)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ariston</t>
+          <t>Eldom</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>technomarket.bg</t>
+          <t>technika.bg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.technomarket.bg/boiler/ariston-velis-pro-50-eu-new-09242822</t>
+          <t>https://technika.bg/product/27638/boyler-eldom-50-l-2-1kw-1-2kw-plosak-dizayn-universalen-montazh-el-upravlenie-emayliran-du060w.html</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>335.46</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>51.1 W x 78.1 H x 27.0 D (horizontal: 78.1 wide x 51.1 high)</t>
+          <t>51.1 W x 83.8 H x 30 D (horizontal: 83.8 long x 51.1 high)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Current NEW version of the specified model; sale price (regular EUR 369); limited stock/last units incl. 2 Sofia stores; 1.5 kW; needs plumber + electrician (dedicated circuit)</t>
+          <t>also OVK Install 729 BGN</t>
         </is>
       </c>
     </row>

--- a/data/shopping.xlsx
+++ b/data/shopping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L153"/>
+  <dimension ref="A1:L154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3467,32 +3467,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Round mirror</t>
+          <t>Round LED mirror (dressing table)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OZZE mirror 60 cm, black frame</t>
+          <t>Round LED mirror D80, black frame, front-lit, touch dimmer 3000/4000/6000K, anti-fog</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OZZE</t>
+          <t>LM Illusion (Varna maker, made to order) or equivalent</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>lampite.bg</t>
+          <t>bazar.bg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.lampite.bg/ogledalo-ozze-o-60-cm-cheren/</t>
+          <t>https://bazar.bg/obiava-49128686/kraglo-ogledalo-s-led-osvetlenie-praktiker</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>D60</t>
+          <t>D80</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Page shows "в наличност". Cheaper: IKEA LINDBYN 50 cm black, EUR 25.51 (-10).</t>
+          <t>Replaces OZZE D60 (too small, no light). Wired from a box behind the mirror at h 130 (on the lighting circuit or the socket circuit with its own touch switch). Any D80 black-frame front-lit LED mirror fits.</t>
         </is>
       </c>
     </row>
@@ -4330,37 +4330,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Decor</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hall mirror</t>
+          <t>Doormat</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LINDBYN mirror 60x120, black</t>
+          <t>NAVR door mat 40x60, coconut natural/black</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>JYSK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ikea.bg</t>
+          <t>jysk.bg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/lindbyn-ogledalo-60x120-sm/30458610/</t>
+          <t>https://jysk.bg/domashni-potrebi/iztrivalki/postelka-za-vrata-navr-40x60kh3-kokos-natural-cherno</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>76.18</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>60x120</t>
+          <t>40x60x3</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Hangs above STÄLL with the bottom edge at 0.92 m (top at about 2.12 m). IKEA BG sells NISSEDAL 65x150 only in white or whitewashed oak, not black. Narrow black option: NISSEDAL 40x150, EUR 30.63. IKEA BG online: InStock (checked 2026-10-22).</t>
+          <t>JYSK BG: listed with add-to-cart (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -4392,37 +4392,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Decor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Doormat</t>
+          <t>Key bowl</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NAVR door mat 40x60, coconut natural/black</t>
+          <t>BLANDA MATT bowl 12 cm, bamboo</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JYSK</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>jysk.bg</t>
+          <t>ikea.bg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://jysk.bg/domashni-potrebi/iztrivalki/postelka-za-vrata-navr-40x60kh3-kokos-natural-cherno</t>
+          <t>https://www.ikea.bg/products/blanda-matt-kupa-za-servirane-bambuk/00222973/</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>40x60x3</t>
+          <t>D12 h6</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>JYSK BG: listed with add-to-cart (checked 2026-10-22).</t>
+          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -4454,17 +4454,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Decor</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Key bowl</t>
+          <t>Wall hooks</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BLANDA MATT bowl 12 cm, bamboo</t>
+          <t>HÖGAFFEL wall hook, black</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/blanda-matt-kupa-za-servirane-bambuk/00222973/</t>
+          <t>https://www.ikea.bg/products/hogaffel-zakachalka-za-stena/70532062/</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>D12 h6</t>
+          <t>single hook</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4516,47 +4516,47 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wall hooks</t>
+          <t>Cordless stick vacuum</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HÖGAFFEL wall hook, black</t>
+          <t>Dyson V8 Absolute (2023), cordless</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ikea.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/hogaffel-zakachalka-za-stena/70532062/</t>
+          <t>https://www.emag.bg/vertikalna-prahosmukachka-bez-kabel-dyson-v8-absolute-2023-425-w-0-54-l-avtonomnost-40-min-zhylt-siv-476547-01/pd/D6KWLDYBM/</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>single hook</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
+          <t>Price taken from the eMAG search listing on 2026-10-22; stock not confirmed. Check that the wall dock is in the box.</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cordless stick vacuum</t>
+          <t>Ironing board</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Dyson V8 Absolute (2023), cordless</t>
+          <t>RUTER ironing board 108x33</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>ikea.bg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/vertikalna-prahosmukachka-bez-kabel-dyson-v8-absolute-2023-425-w-0-54-l-avtonomnost-40-min-zhylt-siv-476547-01/pd/D6KWLDYBM/</t>
+          <t>https://www.ikea.bg/products/ruter-daska-za-gladene-108x33-sm/60471610/</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>108x33, h77-90</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Price taken from the eMAG search listing on 2026-10-22; stock not confirmed. Check that the wall dock is in the box.</t>
+          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ironing board</t>
+          <t>Mop</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RUTER ironing board 108x33</t>
+          <t>PEPPRIG mop</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/ruter-daska-za-gladene-108x33-sm/60471610/</t>
+          <t>https://www.ikea.bg/products/pepprig-mop/40527081/</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>108x33, h77-90</t>
+          <t>L100.5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mop</t>
+          <t>Broom + dustpan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PEPPRIG mop</t>
+          <t>VINDSIKT dustpan and broom, bamboo/grey-green</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/pepprig-mop/40527081/</t>
+          <t>https://www.ikea.bg/products/vindsikt-lopatka-metla/40608063/</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>L100.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Broom + dustpan</t>
+          <t>Step stool</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VINDSIKT dustpan and broom, bamboo/grey-green</t>
+          <t>BEKVÄM step stool, beech</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/vindsikt-lopatka-metla/40608063/</t>
+          <t>https://www.ikea.bg/products/bekvam-stolche-stalba/60178887/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43x39x50</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4821,22 +4821,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Bathroom</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Step stool</t>
+          <t>Bath towels</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BEKVÄM step stool, beech</t>
+          <t>VÅGSJÖN bath towel 70x140, light beige</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4851,22 +4851,22 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/bekvam-stolche-stalba/60178887/</t>
+          <t>https://www.ikea.bg/products/vagsjon-havlia-za-banya/10607319/</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>43x39x50</t>
+          <t>70x140</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bath towels</t>
+          <t>Hand towels</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VÅGSJÖN bath towel 70x140, light beige</t>
+          <t>VÅGSJÖN hand towel 40x70, light beige</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/vagsjon-havlia-za-banya/10607319/</t>
+          <t>https://www.ikea.bg/products/vagsjon-karpa-za-ratse/40607370/</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>70x140</t>
+          <t>40x70</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hand towels</t>
+          <t>Bath mat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VÅGSJÖN hand towel 40x70, light beige</t>
+          <t>TOFTBO bath mat 50x80, beige</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4975,22 +4975,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/vagsjon-karpa-za-ratse/40607370/</t>
+          <t>https://www.ikea.bg/products/toftbo-postelka-za-banya/60610263/</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>40x70</t>
+          <t>50x80</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5012,47 +5012,47 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bath mat</t>
+          <t>Hooks</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TOFTBO bath mat 50x80, beige</t>
+          <t>STOCKVIK hook, black steel (1 pc)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>JYSK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ikea.bg</t>
+          <t>jysk.bg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/toftbo-postelka-za-banya/60610263/</t>
+          <t>https://jysk.bg/banya/aksesoari-za-banya/zakachalki-i-postavki-za-krpi/zakachalki-stockvik-cherna-stomana-1-broy</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>50x80</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
+          <t>JYSK BG: listed with add-to-cart (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -5079,12 +5079,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hooks</t>
+          <t>Toilet roll holder</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>STOCKVIK hook, black steel (1 pc)</t>
+          <t>SUNDSBRUK toilet roll holder, black metal</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://jysk.bg/banya/aksesoari-za-banya/zakachalki-i-postavki-za-krpi/zakachalki-stockvik-cherna-stomana-1-broy</t>
+          <t>https://jysk.bg/banya/aksesoari-za-banya/aksesoari/postavka-za-toaletna-khartiya-sundsbruk-metal-cherna</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5141,32 +5141,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Toilet roll holder</t>
+          <t>Pedal bin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SUNDSBRUK toilet roll holder, black metal</t>
+          <t>Vinoks pedal bin 5 L, soft close, black stainless (COSBLACK)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JYSK</t>
+          <t>Vinoks</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>jysk.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://jysk.bg/banya/aksesoari-za-banya/aksesoari/postavka-za-toaletna-khartiya-sundsbruk-metal-cherna</t>
+          <t>https://www.emag.bg/kosh-za-bokluk-s-pedal-vinoks-5l-soft-close-neryzhdaema-stomana-cheren-za-banja-cosblack/pd/DZB9TY2BM/</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>5 L</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>JYSK BG: listed with add-to-cart (checked 2026-10-22).</t>
+          <t>IKEA and JYSK BG have no black pedal bin. Price from the eMAG listing; stock not confirmed.</t>
         </is>
       </c>
     </row>
@@ -5203,32 +5203,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pedal bin</t>
+          <t>Toilet brush holder</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Vinoks pedal bin 5 L, soft close, black stainless (COSBLACK)</t>
+          <t>GANSJÖN toilet brush, black</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vinoks</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>ikea.bg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/kosh-za-bokluk-s-pedal-vinoks-5l-soft-close-neryzhdaema-stomana-cheren-za-banja-cosblack/pd/DZB9TY2BM/</t>
+          <t>https://www.ikea.bg/products/gansjon-chetka-za-toaletna/60605488/</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>5 L</t>
+          <t>D10 h38</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,29 +5248,29 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>IKEA and JYSK BG have no black pedal bin. Price from the eMAG listing; stock not confirmed.</t>
+          <t>Black plastic, not metal. IKEA BG online: InStock (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Bathroom</t>
+          <t>Balcony</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Toilet brush holder</t>
+          <t>Balcony table + 2 chairs</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GANSJÖN toilet brush, black</t>
+          <t>TÄRNÖ table + 2 chairs, outdoor, black/light brown</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/gansjon-chetka-za-toaletna/60605488/</t>
+          <t>https://www.ikea.bg/products/tarno-masa-2-stola-za-upotreba-na-otkrito/29575342/</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>66.42</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>D10 h38</t>
+          <t>table 55x54 h70; chair 39x40 h79</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Black plastic, not metal. IKEA BG online: InStock (checked 2026-10-22).</t>
+          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -5322,17 +5322,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Flooring</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Balcony table + 2 chairs</t>
+          <t>Decking tiles</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TÄRNÖ table + 2 chairs, outdoor, black/light brown</t>
+          <t>RUNNEN floor decking, outdoor, dark grey (9 pcs = 0.81 m2)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5347,22 +5347,22 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/tarno-masa-2-stola-za-upotreba-na-otkrito/29575342/</t>
+          <t>https://www.ikea.bg/products/runnen-podova-nastilka-9-br-v-k-t/90238111/</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>66.42</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>table 55x54 h70; chair 39x40 h79</t>
+          <t>30x30 tiles; area 2.85x1.15 = 3.28 m2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
+          <t>5 packs = 45 tiles; about 40 needed including cuts. IKEA BG online: InStock (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -5384,17 +5384,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Flooring</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Decking tiles</t>
+          <t>String lights</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>RUNNEN floor decking, outdoor, dark grey (9 pcs = 0.81 m2)</t>
+          <t>SOLVINDEN LED string, 12 bulbs, outdoor, battery, white</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/runnen-podova-nastilka-9-br-v-k-t/90238111/</t>
+          <t>https://www.ikea.bg/products/solvinden-led-girlyanda-s-12-lampichki-na-otkrito-na-baterii/60575981/</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30x30 tiles; area 2.85x1.15 = 3.28 m2</t>
+          <t>see page</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>5 packs = 45 tiles; about 40 needed including cuts. IKEA BG online: InStock (checked 2026-10-22).</t>
+          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
         </is>
       </c>
     </row>
@@ -5446,17 +5446,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Decor</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>String lights</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SOLVINDEN LED string, 12 bulbs, outdoor, battery, white</t>
+          <t>BORRBY lantern for tealight, black</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/solvinden-led-girlyanda-s-12-lampichki-na-otkrito-na-baterii/60575981/</t>
+          <t>https://www.ikea.bg/products/borrby-fener-za-chaena-svesht/60608854/</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>see page</t>
+          <t>11x11 h20</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5508,37 +5508,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Decor</t>
+          <t>Plants</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Plant</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BORRBY lantern for tealight, black</t>
+          <t>Olive tree, pot 15 cm</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>Praktiker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ikea.bg</t>
+          <t>praktiker.bg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.ikea.bg/products/borrby-fener-za-chaena-svesht/60608854/</t>
+          <t>https://praktiker.bg/bg/Ovoshki/MASLINA/p/467136</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>11x11 h20</t>
+          <t>pot D15</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,49 +5558,45 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>IKEA BG online: InStock (checked 2026-10-22).</t>
+          <t>Live plant. Praktiker: InStock.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Balcony</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Plants</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plant</t>
+          <t>Dressing table (custom)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Olive tree, pot 15 cm</t>
+          <t>Wall-hung oak dressing table 140x36 h75.5: 3-drawer pedestal + slim knee drawer, Blum Tip-On</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Praktiker</t>
+          <t>custom joinery</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>praktiker.bg</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://praktiker.bg/bg/Ovoshki/MASLINA/p/467136</t>
-        </is>
-      </c>
+          <t>joiner</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>420.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5610,44 +5606,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>pot D15</t>
+          <t>140x36x75.5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Live plant. Praktiker: InStock.</t>
+          <t>Replaces the 100x30 shelf with one drawer.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Freestanding fridge-freezer</t>
+          <t>Folding airer</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Samsung RB38C650EB1/EF (Total No Frost, Dark Inox, 386 L)</t>
+          <t>Leifheit Pegasus 150 Solid</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Leifheit</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5657,12 +5653,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/hladilnik-samsung-386-l-total-no-frost-all-around-cooling-digitalen-invertoren-kompresor-dispensyr-za-voda-wifi-klas-e-h-203-sm-dark-inox-rb38c650eb1-ef/pd/D80CTKYBM/</t>
+          <t>https://www.emag.bg/search/leifheit%20pegasus%20150</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5672,17 +5668,17 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>59.5 x 203 x 65.8 cm</t>
+          <t>folded 55x6x110</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Model change: Bosch KGN39VXCT (black inox) is listed 'no longer offered' at jarcomputers.bg; emag/technopolis/technomarket have no 60 cm Bosch black-inox 203 cm unit (KGN49VXDT is 70 cm wide). Samsung Dark Inox chosen. Energy class E; has built-in water dispenser (tank, no plumbing). Width/depth from Samsung spec, not shown on emag search page. Alt: Bosch KGN39LBCF black glass 1094.89 EUR on emag.</t>
+          <t>Stored folded behind the bedroom door.</t>
         </is>
       </c>
     </row>
@@ -5699,17 +5695,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fully integrated dishwasher 45 cm</t>
+          <t>Freestanding fridge-freezer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Bosch Serie 4 SPV4EMX17E (10 place settings, class B, Home Connect)</t>
+          <t>Samsung RB38C650EB1/EF (Total No Frost, Dark Inox, 386 L)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5719,12 +5715,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/sydomijalna-za-vgrazhdane-bosch-10-komplekta-6-programi-efficientdry-home-connect-infolight-dosageassist-hygiene-plus-ecosilence-drive-klas-b-45-sm-spv4emx17e/pd/DK72HB2BM/</t>
+          <t>https://www.emag.bg/hladilnik-samsung-386-l-total-no-frost-all-around-cooling-digitalen-invertoren-kompresor-dispensyr-za-voda-wifi-klas-e-h-203-sm-dark-inox-rb38c650eb1-ef/pd/D80CTKYBM/</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>549.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5730,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>44.8 x 81.5 x 55 cm</t>
+          <t>59.5 x 203 x 65.8 cm</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5740,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Needs furniture front panel; needs plumber + dedicated socket.</t>
+          <t>Model change: Bosch KGN39VXCT (black inox) is listed 'no longer offered' at jarcomputers.bg; emag/technopolis/technomarket have no 60 cm Bosch black-inox 203 cm unit (KGN49VXDT is 70 cm wide). Samsung Dark Inox chosen. Energy class E; has built-in water dispenser (tank, no plumbing). Width/depth from Samsung spec, not shown on emag search page. Alt: Bosch KGN39LBCF black glass 1094.89 EUR on emag.</t>
         </is>
       </c>
     </row>
@@ -5761,12 +5757,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Built-in oven 60 cm, black glass</t>
+          <t>Fully integrated dishwasher 45 cm</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Hansa Fine Design BOES68465 (62 L, grill, display, push-up knobs)</t>
+          <t>Hansa ZIM435H fully integrated dishwasher 45 cm (9 place settings, 5 programmes, class E)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5781,12 +5777,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/furni-za-vgrazhdane/brand/hansa/c</t>
+          <t>https://www.emag.bg/sydomijalna-za-vgrazhdane-hansa-9-komplekta-5-programi-klas-e-45-sm-zim435h/pd/D74XZKMBM/</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>173.84</t>
+          <t>331.83</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5796,7 +5792,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>59.4x57.5x59.5</t>
+          <t>44.8 x 81.5 x 55 cm</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5802,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>client choice: Hansa, no microwave function; verify the exact model page/stock on eMAG before buying</t>
+          <t>Budget swap, same brand as oven/hob/hood. In stock (seller Libra Group). Confirm the control panel is hidden (fully integrated) before ordering. Needs furniture front panel, plumber + dedicated socket. Alt: Gorenje GV520E15 319.87 EUR (emag), same size.</t>
         </is>
       </c>
     </row>
@@ -5823,17 +5819,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Induction hob 60 cm, black</t>
+          <t>Built-in oven 60 cm, black glass</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Bosch Serie 4 PUE611BB5E (4 zones, PowerBoost, TouchSelect)</t>
+          <t>Hansa Fine Design BOES68465 (62 L, grill, display, push-up knobs)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Hansa</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5843,12 +5839,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/plot-za-vgrazhdane-bosch-indukcija-4-nagrevatelni-zoni-touchselect-powerboost-restart-tajmer-60-sm-cheren-pue611bb5e/pd/DNB99FMBM/</t>
+          <t>https://www.emag.bg/furni-za-vgrazhdane/brand/hansa/c</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>295.07</t>
+          <t>173.84</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5858,7 +5854,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>59.2 x 5.1 x 52.2 cm (cut-out 56 x 49)</t>
+          <t>59.4x57.5x59.5</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5864,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Needs electrician (7.4 kW, 3x2.5 mm2 / 32 A or 2-phase). Dims from Bosch spec.</t>
+          <t>client choice: Hansa, no microwave function; verify the exact model page/stock on eMAG before buying</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5881,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Telescopic hood 60 cm, black, recirculation</t>
+          <t>Domino hob 30 cm, 2 zones, black</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Hansa OTP 6243 BGH (telescopic, 350 m3/h, black glass)</t>
+          <t>Hansa BHC36177 (vitroceramic, 2 zones, touch, timer, 3 kW)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5900,17 +5896,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>vimax.bg / home-max.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://vimax.bg/absorbator-za-vgrazhdane-hansa-otp-6243-bgh.html</t>
+          <t>https://www.emag.bg/plot-za-vgrazhdane-hansa-vitrokeramika-2-zoni-za-gotvene-touch-control-tajmer-30-sm-cheren-bhc36177/pd/DHJRPHBBM/</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>111.97</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5920,17 +5916,17 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>60 cm, built into the 60 wall unit over the hob</t>
+          <t>28.8 x 51</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>verify price</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>cheapest offer ~102.92 EUR (pazaruvaj); add the matching carbon filter for recirculation</t>
+          <t>Budget choice (same brand as oven and hood). 3 kW single phase: 230 V / 16-20 A, 3x2.5 mm2.</t>
         </is>
       </c>
     </row>
@@ -5947,12 +5943,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Carbon filter for the Hansa hood</t>
+          <t>Telescopic hood 60 cm, black, recirculation</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Hansa / Amica carbon filter for OTP6243 (check the code on the hood manual)</t>
+          <t>Hansa OTP 6243 BGH (telescopic, 350 m3/h, black glass)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5962,17 +5958,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>hansabg.org / emag.bg</t>
+          <t>vimax.bg / home-max.bg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/absorbatori/brand/hansa/c</t>
+          <t>https://vimax.bg/absorbator-za-vgrazhdane-hansa-otp-6243-bgh.html</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>111.97</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5978,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>60 cm, built into the 60 wall unit over the hob</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5988,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>approx. price - confirm</t>
+          <t>cheapest offer ~102.92 EUR (pazaruvaj); add the matching carbon filter for recirculation</t>
         </is>
       </c>
     </row>
@@ -6009,32 +6005,32 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bean-to-cup coffee machine &lt;=24 cm wide</t>
+          <t>Carbon filter for the Hansa hood</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>De'Longhi Magnifica S ECAM22.110.SB</t>
+          <t>Hansa / Amica carbon filter for OTP6243 (check the code on the hood manual)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>De'Longhi</t>
+          <t>Hansa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>technopolis.bg</t>
+          <t>hansabg.org / emag.bg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.technopolis.bg/en/Kafeavtomati/Kafeavtomat-DELONGHI-MAGNIFICA-S-ECAM22-110-SB/p/824292</t>
+          <t>https://www.emag.bg/absorbatori/brand/hansa/c</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>460.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6044,7 +6040,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>23 x 34 x 43 cm (listing; De'Longhi spec 23.8 W)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6054,7 +6050,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>In stock. Colour is silver/black front (listed 'grey'); all-black ECAM22.110.B only found on emag at 646.25 EUR (overpriced) - chose SB.</t>
+          <t>approx. price - confirm</t>
         </is>
       </c>
     </row>
@@ -6071,17 +6067,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Electric kettle, black</t>
+          <t>Bean-to-cup coffee machine &lt;=24 cm wide</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Bosch TWK70B03 (1.7 L, black glass)</t>
+          <t>De'Longhi Magnifica S ECAM22.110.SB</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>De'Longhi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6091,12 +6087,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.technopolis.bg/bg/Elektricheski-kani/Elektricheska-kana-BOSCH-TWK70B03/p/803846</t>
+          <t>https://www.technopolis.bg/en/Kafeavtomati/Kafeavtomat-DELONGHI-MAGNIFICA-S-ECAM22-110-SB/p/824292</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>460.1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6106,7 +6102,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>23 x 34 x 43 cm (listing; De'Longhi spec 23.8 W)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6112,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Price seen in search results (page 404 on direct fetch). Cheaper black alt: Bosch MyMoment TWK1M123 35.90 EUR at technopolis.</t>
+          <t>In stock. Colour is silver/black front (listed 'grey'); all-black ECAM22.110.B only found on emag at 646.25 EUR (overpriced) - chose SB.</t>
         </is>
       </c>
     </row>
@@ -6128,22 +6124,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sanitaryware</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Black granite sink, single bowl, for 50 cm cabinet</t>
+          <t>Electric kettle, black</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Teka Stone 50 B-TG (black metallic, reversible, with drainer)</t>
+          <t>Philips HD9318/20 kettle 1.7 L, black</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Teka</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6153,12 +6149,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/kuhnenska-mivka-teka-stone-50-b-tg-860-x-510-cheren-metalik-granitna-za-vgrazhdane-obryshtaema-za-shkaf-50-sm-kxg0102823/pd/DMJ099MBM/</t>
+          <t>https://www.emag.bg/elektricheska-kana-philips-mikrofiltyr-2400-w-plastmasa-1-7-l-cherna-hd9318-20/pd/DKH42YMBM/</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>223.76</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6168,7 +6164,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>86 x 51 cm, bowl 38 x 41.4 x 20 cm, cut-out ~84 x 48</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6178,7 +6174,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Price from search result (emag page blocked on fetch). Wider-bowl alt: Teka Menorca 50 S-TG black metallic (49 x 51, bowl 43.5 x 37.5, no drainer) at siko.bg 529.17 BGN / ~270.56 EUR (page rate-limited). Needs plumber.</t>
+          <t>Budget swap for Bosch TWK70B03. Price from eMAG listing, in stock. Alt: Tefal KO2008 black 27.41 EUR.</t>
         </is>
       </c>
     </row>
@@ -6195,12 +6191,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kitchen tap, black</t>
+          <t>Black granite sink, single bowl, for 50 cm cabinet</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Teka 934 black, single-lever, swivel spout</t>
+          <t>Teka Stone 50 B-TG (black metallic, reversible, with drainer)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6210,17 +6206,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>praktiker.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Smesiteli-za-kuhnya/SMESITEL-ZA-KUHNYa-S-PODVIZhNO-RAMO-TEKA-934-ChEREN/p/493588</t>
+          <t>https://www.emag.bg/kuhnenska-mivka-teka-stone-50-b-tg-860-x-510-cheren-metalik-granitna-za-vgrazhdane-obryshtaema-za-shkaf-50-sm-kxg0102823/pd/DMJ099MBM/</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>122.7</t>
+          <t>223.76</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6226,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>86 x 51 cm, bowl 38 x 41.4 x 20 cm, cut-out ~84 x 48</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6240,7 +6236,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>In stock, 72-month warranty. Search snippet showed promo 105.00 EUR; page shows 122.70. Alt: Grohe Eurosmart matte black 137 EUR at siko.bg.</t>
+          <t>Price from search result (emag page blocked on fetch). Wider-bowl alt: Teka Menorca 50 S-TG black metallic (49 x 51, bowl 43.5 x 37.5, no drainer) at siko.bg 529.17 BGN / ~270.56 EUR (page rate-limited). Needs plumber.</t>
         </is>
       </c>
     </row>
@@ -6252,37 +6248,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fitting</t>
+          <t>Sanitaryware</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Waste sorting for 60 cm sink base</t>
+          <t>Kitchen tap, black</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GTV Axispace PB-AS-600 drawer-insert bin, 1x15 L + 3x7 L</t>
+          <t>Teka 934 black, single-lever, swivel spout</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GTV</t>
+          <t>Teka</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>praktiker.bg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/koshche-za-bokluk-gtv-axispace-vgradeno-v-chekmedzheto-s-3-otdelenija-x-7l-i-1-otdelenie-x-15l-za-shkaf-600-mm-pb-as-600-1x15l-3x7l/pd/D1B1P03BM/</t>
+          <t>https://praktiker.bg/bg/Smesiteli-za-kuhnya/SMESITEL-ZA-KUHNYa-S-PODVIZhNO-RAMO-TEKA-934-ChEREN/p/493588</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>61.88</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6292,7 +6288,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>for 60 cm cabinet (drawer insert)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6302,7 +6298,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No 2x18+8 L 60 cm unit found in stock in BG. Hailo Cargo 600 (2x28 / 2x13+28 L) at prodes.bg from 374.86 EUR is OUT OF STOCK. Colour not stated (Axispace usually grey/graphite).</t>
+          <t>In stock, 72-month warranty. Search snippet showed promo 105.00 EUR; page shows 122.70. Alt: Grohe Eurosmart matte black 137 EUR at siko.bg.</t>
         </is>
       </c>
     </row>
@@ -6319,32 +6315,32 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Corner unit pull-out (LeMans)</t>
+          <t>Waste sorting for 60 cm sink base</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Kesseboehmer LeMans II 450 mm, ARENAplus pure, anthracite (left; right version same price) + connecting element</t>
+          <t>GTV Axispace PB-AS-600 drawer-insert bin, 1x15 L + 3x7 L</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kesseboehmer</t>
+          <t>GTV</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>salex.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://salex.bg/m-m-babrekoviden-lemansii-450mm-desen-arenaplus-pure-antracit-37249/</t>
+          <t>https://www.emag.bg/koshche-za-bokluk-gtv-axispace-vgradeno-v-chekmedzheto-s-3-otdelenija-x-7l-i-1-otdelenie-x-15l-za-shkaf-600-mm-pb-as-600-1x15l-3x7l/pd/D1B1P03BM/</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>481.58</t>
+          <t>61.88</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6354,7 +6350,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>450 mm unit (kit incl. connector for 600-750 mm deep corner)</t>
+          <t>for 60 cm cabinet (drawer insert)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6364,7 +6360,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Anthracite, in stock. Choose left/right per corner hand. Optional LED kit 88.85 EUR (salex).</t>
+          <t>No 2x18+8 L 60 cm unit found in stock in BG. Hailo Cargo 600 (2x28 / 2x13+28 L) at prodes.bg from 374.86 EUR is OUT OF STOCK. Colour not stated (Axispace usually grey/graphite).</t>
         </is>
       </c>
     </row>
@@ -6381,32 +6377,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cutlery insert for 55 cm cabinet drawer</t>
+          <t>Corner unit pull-out (LeMans)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CLASStitude adjustable cutlery organiser, 8 compartments, black</t>
+          <t>Kesseboehmer LeMans II 450 mm, ARENAplus pure, anthracite (left; right version same price) + connecting element</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CLASStitude</t>
+          <t>Kesseboehmer</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>salex.bg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/organajzer-za-pribori-i-kuhnenski-pribori-s-8-otdelenija-classtitude-reguliruemo-chekmedzhe-l-s-dylzhina-33-57-sm-i-l-shirina-38-sm-reguliruema-postavka-za-nozhove-lyzhici-i-vilici-prostoren-izraboten/pd/D6SD9D3BM/</t>
+          <t>https://salex.bg/m-m-babrekoviden-lemansii-450mm-desen-arenaplus-pure-antracit-37249/</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>481.58</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6416,7 +6412,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>38 W x 33-57 L cm (extendable, not cut-to-size)</t>
+          <t>450 mm unit (kit incl. connector for 600-750 mm deep corner)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6422,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Extendable, not cut-to-size. Fitted alternative: GTV Axispace black for 600 mm cabinet 18.06 EUR (emag) - too wide for 55 cm. Prefer 60 cm drawer cabinet if a fitted insert is wanted.</t>
+          <t>Anthracite, in stock. Choose left/right per corner hand. Optional LED kit 88.85 EUR (salex).</t>
         </is>
       </c>
     </row>
@@ -6438,37 +6434,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>Fitting</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LED strip 3000 K, 24 V, 5 m roll</t>
+          <t>Cutlery insert for 55 cm cabinet drawer</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>D-IL LED strip 24V 3000K 120 LED/m IP20, 5 m</t>
+          <t>CLASStitude adjustable cutlery organiser, 8 compartments, black</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>D-IL</t>
+          <t>CLASStitude</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>praktiker.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/LED-lenti-i-aksesoari/LED-LENTA-12W-5M-24V-3000K-120-1-IP20-D-IL/p/245680</t>
+          <t>https://www.emag.bg/organajzer-za-pribori-i-kuhnenski-pribori-s-8-otdelenija-classtitude-reguliruemo-chekmedzhe-l-s-dylzhina-33-57-sm-i-l-shirina-38-sm-reguliruema-postavka-za-nozhove-lyzhici-i-vilici-prostoren-izraboten/pd/D6SD9D3BM/</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6478,7 +6474,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>5 m roll (cut to ~4.5 m)</t>
+          <t>38 W x 33-57 L cm (extendable, not cut-to-size)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6484,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Price per 5 m roll, in stock. Listing says '12W' (likely W/m -&gt; ~54 W for 4.5 m). Higher-CRI alt: Optonica COB 24V 3000K Ra90 10 W/m 19.38 EUR/37.90 BGN (search result).</t>
+          <t>Extendable, not cut-to-size. Fitted alternative: GTV Axispace black for 600 mm cabinet 18.06 EUR (emag) - too wide for 55 cm. Prefer 60 cm drawer cabinet if a fitted insert is wanted.</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6501,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Aluminium LED profile, black, 2 m</t>
+          <t>LED strip 3000 K, 24 V, 5 m roll</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>D-IL aluminium profile U-shaped, matt black, 2 m</t>
+          <t>D-IL LED strip 24V 3000K 120 LED/m IP20, 5 m</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6525,22 +6521,22 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/LED-lenti-i-aksesoari/ALUMINIEV-PROFIL-ZA-LED-LENTA-P-OBRAZEN-ChEREN-MAT-2M-D-IL/p/232078</t>
+          <t>https://praktiker.bg/bg/LED-lenti-i-aksesoari/LED-LENTA-12W-5M-24V-3000K-120-1-IP20-D-IL/p/245680</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>200 cm each (3 pcs = 6 m, cut to 4.5 m)</t>
+          <t>5 m roll (cut to ~4.5 m)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6546,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Price per 2 m piece, in stock. Diffuser not stated on page - confirm included, else buy separately.</t>
+          <t>Price per 5 m roll, in stock. Listing says '12W' (likely W/m -&gt; ~54 W for 4.5 m). Higher-CRI alt: Optonica COB 24V 3000K Ra90 10 W/m 19.38 EUR/37.90 BGN (search result).</t>
         </is>
       </c>
     </row>
@@ -6567,17 +6563,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LED driver 24 V</t>
+          <t>Aluminium LED profile, black, 2 m</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Vivalux LED power supply 60W 24V</t>
+          <t>D-IL aluminium profile U-shaped, matt black, 2 m</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vivalux</t>
+          <t>D-IL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6587,22 +6583,22 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/en/LED-lenti-i-aksesoari/ZAHRANVANE-LED-LENTA-60W-24V-VIVALUX/p/148508</t>
+          <t>https://praktiker.bg/bg/LED-lenti-i-aksesoari/ALUMINIEV-PROFIL-ZA-LED-LENTA-P-OBRAZEN-ChEREN-MAT-2M-D-IL/p/232078</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>16 x 4 x 3.1 cm</t>
+          <t>200 cm each (3 pcs = 6 m, cut to 4.5 m)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6612,49 +6608,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>In stock. Needs electrician (switched supply, place driver in ventilated cabinet).</t>
+          <t>Price per 2 m piece, in stock. Diffuser not stated on page - confirm included, else buy separately.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bathroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wall-hung rimless WC pan + soft-close seat</t>
+          <t>LED driver 24 V</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Cersanit Moduo CleanOn wall-hung rimless WC with slim duroplast soft-close seat (Bauhaus art. 60696175)</t>
+          <t>Vivalux LED power supply 60W 24V</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cersanit</t>
+          <t>Vivalux</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>bauhaus.bg</t>
+          <t>praktiker.bg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://bauhaus.bg/stenna-toaletna-bez-rab-cersanit-moduo-cleanon/p/122979</t>
+          <t>https://praktiker.bg/en/LED-lenti-i-aksesoari/ZAHRANVANE-LED-LENTA-60W-24V-VIVALUX/p/148508</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6664,7 +6660,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>52.5 x 36 x 38 cm</t>
+          <t>16 x 4 x 3.1 cm</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6670,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>White gloss ceramic, seat included. In stock (7). BGN converted. Needs plumber.</t>
+          <t>In stock. Needs electrician (switched supply, place driver in ventilated cabinet).</t>
         </is>
       </c>
     </row>
@@ -6691,32 +6687,32 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Concealed WC frame</t>
+          <t>Wall-hung rimless WC pan + soft-close seat</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Geberit Duofix 112 cm with Delta 12 cm cistern + Delta01 chrome plate (Praktiker 244980, EAN 4064746032608)</t>
+          <t>Cersanit Moduo CleanOn wall-hung rimless WC with slim duroplast soft-close seat (Bauhaus art. 60696175)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Geberit</t>
+          <t>Cersanit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>praktiker.bg</t>
+          <t>bauhaus.bg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Strukturi-i-komplekti-za-vgrazhdane/STRUKTURA-ZA-VGRAZhDANE-GEBERIT/p/244980</t>
+          <t>https://bauhaus.bg/stenna-toaletna-bez-rab-cersanit-moduo-cleanon/p/122979</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>229.99</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6726,7 +6722,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>50 x 112 cm, 12 cm cistern</t>
+          <t>52.5 x 36 x 38 cm</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6732,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Includes chrome Delta01 plate (replace with black 11c). Delta cistern takes Delta-series plates only. Alt: Bauhaus Duofix Delta p/110422 at 255.13 EUR. BGN converted. Needs plumber.</t>
+          <t>White gloss ceramic, seat included. In stock (7). BGN converted. Needs plumber.</t>
         </is>
       </c>
     </row>
@@ -6753,12 +6749,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Flush plate, matt black</t>
+          <t>Concealed WC frame</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Geberit Delta50 dual-flush plate, matt black, 115.119.14.1</t>
+          <t>Geberit Duofix 112 cm with Delta 12 cm cistern + Delta01 chrome plate (Praktiker 244980, EAN 4064746032608)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6768,17 +6764,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>praktiker.bg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/klapa-za-zadejstvane-na-vgradeno-wc-kazanche-geberit-delta50-za-izmivane-s-dva-obema-voda-cheren-mat-geb115-119-14-1/pd/DHJHZ2YBM/</t>
+          <t>https://praktiker.bg/bg/Strukturi-i-komplekti-za-vgrazhdane/STRUKTURA-ZA-VGRAZhDANE-GEBERIT/p/244980</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>69.99</t>
+          <t>229.99</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6788,7 +6784,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>approx 24.6 x 16.4 cm</t>
+          <t>50 x 112 cm, 12 cm cistern</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6798,7 +6794,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Seen on eMAG search listing, product page not opened. Size from Geberit spec, not the shop. BGN converted.</t>
+          <t>Includes chrome Delta01 plate (replace with black 11c). Delta cistern takes Delta-series plates only. Alt: Bauhaus Duofix Delta p/110422 at 255.13 EUR. BGN converted. Needs plumber.</t>
         </is>
       </c>
     </row>
@@ -6810,37 +6806,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thermostatic shower system, black</t>
+          <t>Flush plate, matt black</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GROHE Tempesta System 250 with thermostat, matt black, 266702431</t>
+          <t>Geberit Delta50 dual-flush plate, matt black, 115.119.14.1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Grohe</t>
+          <t>Geberit</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>siko.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://siko.bg/promo-shower-system-grohe-tempesta-250-with-thermostat-266702431</t>
+          <t>https://www.emag.bg/klapa-za-zadejstvane-na-vgradeno-wc-kazanche-geberit-delta50-za-izmivane-s-dva-obema-voda-cheren-mat-geb115-119-14-1/pd/DHJHZ2YBM/</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>495.0</t>
+          <t>69.99</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6850,7 +6846,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>head 25 cm, hand shower 11 cm</t>
+          <t>approx 24.6 x 16.4 cm</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6860,7 +6856,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Exposed thermostat with head/hand switch per Grohe spec (not stated on page). Hand shower holder on riser, not a separate rail. In stock. BGN converted. Needs plumber.</t>
+          <t>Seen on eMAG search listing, product page not opened. Size from Geberit spec, not the shop. BGN converted.</t>
         </is>
       </c>
     </row>
@@ -6877,32 +6873,32 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Linear shower drain 70 cm, black</t>
+          <t>Thermostatic shower system, black</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ferro Slim Pro OLSP1-70-BL linear drain, black stainless, DN40</t>
+          <t>GROHE Tempesta System 250 with thermostat, matt black, 266702431</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ferro</t>
+          <t>Grohe</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>siko.bg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/lineen-sifon-ferro-slim-pro-olsp1-70-bl-neryzhdaema-stomana-dylzhina-700-mm-vgraden-sifon-dn40-membranna-izolacija-cheren-ferolsp1-70-bl/pd/D25NMFMBM/</t>
+          <t>https://siko.bg/promo-shower-system-grohe-tempesta-250-with-thermostat-266702431</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>216.45</t>
+          <t>495.0</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6912,7 +6908,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>70 cm</t>
+          <t>head 25 cm, hand shower 11 cm</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6922,7 +6918,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Available to order only (при заявка). Alt in stock: Camargue 70 cm with black glass grate, Bauhaus p/18254, 219.34 EUR. BGN converted. Needs plumber/tiler.</t>
+          <t>Exposed thermostat with head/hand switch per Grohe spec (not stated on page). Hand shower holder on riser, not a separate rail. In stock. BGN converted. Needs plumber.</t>
         </is>
       </c>
     </row>
@@ -6939,17 +6935,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bi-fold shower door 90 cm, black</t>
+          <t>Linear shower drain 70 cm, black</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Rea Rapid Fold 90 black, REA-K6419</t>
+          <t>Ferro Slim Pro OLSP1-70-BL linear drain, black stainless, DN40</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rea</t>
+          <t>Ferro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6959,12 +6955,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/vrata-za-dush-rea-rapid-ford-90-sgyvane-zakaleno-styklo-cheren-rea-k6419/pd/D5MRDW3BM/</t>
+          <t>https://www.emag.bg/lineen-sifon-ferro-slim-pro-olsp1-70-bl-neryzhdaema-stomana-dylzhina-700-mm-vgraden-sifon-dn40-membranna-izolacija-cheren-ferolsp1-70-bl/pd/D25NMFMBM/</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>216.45</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6974,7 +6970,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>90 x 190 cm, 6 mm glass</t>
+          <t>70 cm</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6980,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sold by a marketplace seller (Podlasiak), in stock. Fits linear-drain floor. BGN converted.</t>
+          <t>Available to order only (при заявка). Alt in stock: Camargue 70 cm with black glass grate, Bauhaus p/18254, 219.34 EUR. BGN converted. Needs plumber/tiler.</t>
         </is>
       </c>
     </row>
@@ -7001,12 +6997,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fixed side panel, black</t>
+          <t>Bi-fold shower door 90 cm, black</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Rea Bler 90 black shower screen, REA-K7638</t>
+          <t>Rea Rapid Fold 90 black, REA-K6419</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7021,12 +7017,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/paravan-za-dush-rea-bler-90-zakaleno-styklo-cheren-rea-k7638/pd/DZF578MBM/</t>
+          <t>https://www.emag.bg/vrata-za-dush-rea-rapid-ford-90-sgyvane-zakaleno-styklo-cheren-rea-k6419/pd/D5MRDW3BM/</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7036,7 +7032,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>90 x 195 cm, 8 mm glass</t>
+          <t>90 x 190 cm, 6 mm glass</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7046,7 +7042,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No black side wall matching Rapid Fold found in BG shops. Check how it joins the door before buying, or ask the seller for the Rapid side wall. Fallback: custom glass panel.</t>
+          <t>Sold by a marketplace seller (Podlasiak), in stock. Fits linear-drain floor. BGN converted.</t>
         </is>
       </c>
     </row>
@@ -7058,37 +7054,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Appliance</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Built-in washer-dryer</t>
+          <t>Fixed side panel, black</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Electrolux EW7W368SI</t>
+          <t>Rea Bler 90 black shower screen, REA-K7638</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Electrolux</t>
+          <t>Rea</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>technopolis.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.technopolis.bg/en/Peralni-sas-sushilni-za-vgrazhdane/PERALNYa-SAS-SUShILNYa--ELECTROLUX-EW7W368SI/p/653332</t>
+          <t>https://www.emag.bg/paravan-za-dush-rea-bler-90-zakaleno-styklo-cheren-rea-k7638/pd/DZF578MBM/</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>914.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7098,7 +7094,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>82 x 60 x 55 cm</t>
+          <t>90 x 195 cm, 8 mm glass</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7108,7 +7104,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8 kg wash / 4 kg dry, 1600 rpm. Also at Technomarket for 915 EUR. Needs plumber and electrician; needs cabinet door.</t>
+          <t>No black side wall matching Rapid Fold found in BG shops. Check how it joins the door before buying, or ask the seller for the Rapid side wall. Fallback: custom glass panel.</t>
         </is>
       </c>
     </row>
@@ -7125,32 +7121,32 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Water heater, flat 60 L, horizontal mounting</t>
+          <t>Built-in washer-dryer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Eldom Galant DU060W (60 L, 2.1+1.2 kW, universal mounting, el. control)</t>
+          <t>Electrolux EW7W368SI</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Eldom</t>
+          <t>Electrolux</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>technika.bg</t>
+          <t>technopolis.bg</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://technika.bg/product/27638/boyler-eldom-50-l-2-1kw-1-2kw-plosak-dizayn-universalen-montazh-el-upravlenie-emayliran-du060w.html</t>
+          <t>https://www.technopolis.bg/en/Peralni-sas-sushilni-za-vgrazhdane/PERALNYa-SAS-SUShILNYa--ELECTROLUX-EW7W368SI/p/653332</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>335.46</t>
+          <t>914.0</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7160,7 +7156,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>51.1 W x 83.8 H x 30 D (horizontal: 83.8 long x 51.1 high)</t>
+          <t>82 x 60 x 55 cm</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7170,7 +7166,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>also OVK Install 729 BGN</t>
+          <t>8 kg wash / 4 kg dry, 1600 rpm. Also at Technomarket for 915 EUR. Needs plumber and electrician; needs cabinet door.</t>
         </is>
       </c>
     </row>
@@ -7182,37 +7178,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Heating</t>
+          <t>Appliance</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Electric towel rail, black, ~50x100</t>
+          <t>Water heater, flat 60 L, horizontal mounting</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Atlantic Doris Wi-Fi 500 W black, thermo-fluid, weekly programming (art. 850476)</t>
+          <t>Eldom Galant DU060W (60 L, 2.1+1.2 kW, universal mounting, el. control)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Eldom</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>technika.bg</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/elektricheska-lira-z-a-banja-atlantic-doris-wi-fi-500-w-cherna-termofluid-sedmichno-programirane-850476/pd/D41LNB2BM/</t>
+          <t>https://technika.bg/product/27638/boyler-eldom-50-l-2-1kw-1-2kw-plosak-dizayn-universalen-montazh-el-upravlenie-emayliran-du060w.html</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>349.0</t>
+          <t>335.46</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7222,7 +7218,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>50 W x 105 H x 10 D</t>
+          <t>51.1 W x 83.8 H x 30 D (horizontal: 83.8 long x 51.1 high)</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7232,7 +7228,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>In stock; BGN converted at 1.95583; needs electrician (fused spur/connection box, zone rules)</t>
+          <t>also OVK Install 729 BGN</t>
         </is>
       </c>
     </row>
@@ -7244,37 +7240,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tap</t>
+          <t>Heating</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wall-mounted basin mixer, matt black, concealed (in-wall)</t>
+          <t>Electric towel rail, black, ~50x100</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Imex Line built-in basin mixer GLD038/NG (Черен мат)</t>
+          <t>Atlantic Doris Wi-Fi 500 W black, thermo-fluid, weekly programming (art. 850476)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Imex</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>feniks.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://feniks.bg/produkti/vgraden-smesitel-za-mivka-line/</t>
+          <t>https://www.emag.bg/elektricheska-lira-z-a-banja-atlantic-doris-wi-fi-500-w-cherna-termofluid-sedmichno-programirane-850476/pd/D41LNB2BM/</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>219.86</t>
+          <t>349.0</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7284,7 +7280,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>wall-mounted, brass, ceramic cartridge</t>
+          <t>50 W x 105 H x 10 D</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7294,7 +7290,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Variant 'Черен мат' art. GLD038/NG listed 'Налично'. Page does not say whether the concealed body is included (Imex in-wall sets usually ship with it) - confirm with Feniks before ordering. Grohe/Hansgrohe black in-wall sets could not be verified in BG shops (eMAG blocked/rate-limited). Needs plumber.</t>
+          <t>In stock; BGN converted at 1.95583; needs electrician (fused spur/connection box, zone rules)</t>
         </is>
       </c>
     </row>
@@ -7306,37 +7302,37 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mirror cabinet</t>
+          <t>Tap</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mirror cabinet with LED, ~60x75x17</t>
+          <t>Wall-mounted basin mixer, matt black, concealed (in-wall)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Inter Ceramic Монца mirror cabinet with lighting (art. 235684)</t>
+          <t>Imex Line built-in basin mixer GLD038/NG (Черен мат)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Inter Ceramic</t>
+          <t>Imex</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>praktiker.bg</t>
+          <t>feniks.bg</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Mebeli/ShKAF-ZA-BANYa-S-OGLEDALO-INTER-CERAMIC-MONTzA/p/235684</t>
+          <t>https://feniks.bg/produkti/vgraden-smesitel-za-mivka-line/</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>219.86</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7346,7 +7342,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>60 x 70 x 17 cm</t>
+          <t>wall-mounted, brass, ceramic cartridge</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7356,7 +7352,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No 60x75x17 LED cabinet found; closest stock item. Lighting 'ДА' per spec, white body. Alternative: Висота Лили 60x65x15.3 LED, 153.30 EUR (praktiker p/132464). Treat as custom if 75 cm is mandatory. Needs electrician for LED feed.</t>
+          <t>Variant 'Черен мат' art. GLD038/NG listed 'Налично'. Page does not say whether the concealed body is included (Imex in-wall sets usually ship with it) - confirm with Feniks before ordering. Grohe/Hansgrohe black in-wall sets could not be verified in BG shops (eMAG blocked/rate-limited). Needs plumber.</t>
         </is>
       </c>
     </row>
@@ -7368,37 +7364,37 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Extract fan</t>
+          <t>Mirror cabinet</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Extract fan 100 mm, timer + humidistat, non-return flap, black</t>
+          <t>Mirror cabinet with LED, ~60x75x17</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Vents 100 Quiet TH black (100QUIETTH BLK)</t>
+          <t>Inter Ceramic Монца mirror cabinet with lighting (art. 235684)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vents</t>
+          <t>Inter Ceramic</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>emag.bg</t>
+          <t>praktiker.bg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/ventilator-za-banja-vents-quiet-th-100-mm-cheren-100quietth-blk/pd/DH8WZ6MBM/</t>
+          <t>https://praktiker.bg/bg/Mebeli/ShKAF-ZA-BANYa-S-OGLEDALO-INTER-CERAMIC-MONTzA/p/235684</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7408,7 +7404,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>dia 100 mm, 97 m3/h</t>
+          <t>60 x 70 x 17 cm</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7418,7 +7414,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Price 87.58 EUR, in stock, from eMAG search results; product page fetch blocked. Specs per eMAG page of the white version (88.53 EUR, temporarily out of stock). Fallback: Vents Quiet 100 TH white 122.94 EUR (emag DKZKN22BM). Cata E-100 GTH at Praktiker (112.48 EUR) rejected: no flap. Needs electrician.</t>
+          <t>No 60x75x17 LED cabinet found; closest stock item. Lighting 'ДА' per spec, white body. Alternative: Висота Лили 60x65x15.3 LED, 153.30 EUR (praktiker p/132464). Treat as custom if 75 cm is mandatory. Needs electrician for LED feed.</t>
         </is>
       </c>
     </row>
@@ -7430,47 +7426,47 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tiles</t>
+          <t>Extract fan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Floor tile Star Gres Town Antracite 60x60 (matt)</t>
+          <t>Extract fan 100 mm, timer + humidistat, non-return flap, black</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Star Gres Town Antracite 60x60 cm, art. 119779, EAN 5901503200940</t>
+          <t>Vents 100 Quiet TH black (100QUIETTH BLK)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Star Gres</t>
+          <t>Vents</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>praktiker.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Granitogres/GRANITOGRES-STAR-GRES-TOWN-ANTRACITE-60X60-CM/p/119779</t>
+          <t>https://www.emag.bg/ventilator-za-banja-vents-quiet-th-100-mm-cheren-100quietth-blk/pd/DH8WZ6MBM/</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>60 x 60 cm</t>
+          <t>dia 100 mm, 97 m3/h</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7476,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Price per m2 (31.28 EUR per pack of 1.8 m2). Qty 5.4 m2 = 3 packs (8% over 5 m2); buy a 4th pack (7.2 m2) for full 10% waste. Online note: extended delivery, order in Praktiker hypermarkets; 53 in stock.</t>
+          <t>Price 87.58 EUR, in stock, from eMAG search results; product page fetch blocked. Specs per eMAG page of the white version (88.53 EUR, temporarily out of stock). Fallback: Vents Quiet 100 TH white 122.94 EUR (emag DKZKN22BM). Cata E-100 GTH at Praktiker (112.48 EUR) rejected: no flap. Needs electrician.</t>
         </is>
       </c>
     </row>
@@ -7497,17 +7493,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wall tile 60x120, warm light grey</t>
+          <t>Floor tile Star Gres Town Antracite 60x60 (matt)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>KAI Клей сив (Clay grey) 60x120 cm rectified, art. 259303</t>
+          <t>Star Gres Town Antracite 60x60 cm, art. 119779, EAN 5901503200940</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KAI</t>
+          <t>Star Gres</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7517,22 +7513,22 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Granitogres/GRANITOGRES-KAI-KLEY-SIV-60H120-CM/p/259303</t>
+          <t>https://praktiker.bg/bg/Granitogres/GRANITOGRES-STAR-GRES-TOWN-ANTRACITE-60X60-CM/p/119779</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>60 x 120 cm</t>
+          <t>60 x 60 cm</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7542,7 +7538,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Price per m2 (33.11 EUR per pack of 1.44 m2). Qty 20.16 m2 = 14 packs. Alternative: KAI Чименто силвър 60x120, 21.49 EUR/m2 (p/244769). Check tone in store.</t>
+          <t>Price per m2 (31.28 EUR per pack of 1.8 m2). Qty 5.4 m2 = 3 packs (8% over 5 m2); buy a 4th pack (7.2 m2) for full 10% waste. Online note: extended delivery, order in Praktiker hypermarkets; 53 in stock.</t>
         </is>
       </c>
     </row>
@@ -7554,22 +7550,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tile adhesive</t>
+          <t>Tiles</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tile adhesive C2TE S1, 25 kg</t>
+          <t>Wall tile 60x120, warm light grey</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ceresit CM 17 сив 25 kg (C2 TE S1)</t>
+          <t>KAI Клей сив (Clay grey) 60x120 cm rectified, art. 259303</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ceresit</t>
+          <t>KAI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7579,22 +7575,22 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Lepila-za-plochki/LEPILO-ZA-PLOChKI-CERESIT-CM-17-SIV/p/435452</t>
+          <t>https://praktiker.bg/bg/Granitogres/GRANITOGRES-KAI-KLEY-SIV-60H120-CM/p/259303</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20.16</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>25 kg bag</t>
+          <t>60 x 120 cm</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7604,7 +7600,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Price per 25 kg bag. About 6 kg/m2 x 26 m2 with back-buttering for large format = 7 bags. Alt: Mapei Keraflex Maxi S1 Zero 19.49 EUR (p/130281).</t>
+          <t>Price per m2 (33.11 EUR per pack of 1.44 m2). Qty 20.16 m2 = 14 packs. Alternative: KAI Чименто силвър 60x120, 21.49 EUR/m2 (p/244769). Check tone in store.</t>
         </is>
       </c>
     </row>
@@ -7616,17 +7612,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Grout</t>
+          <t>Tile adhesive</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Grout for floor (charcoal), 2 kg</t>
+          <t>Tile adhesive C2TE S1, 25 kg</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ceresit CE 40 Въглен (18) 2 kg</t>
+          <t>Ceresit CM 17 сив 25 kg (C2 TE S1)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7641,22 +7637,22 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Fugi/FUGIRAShtA-SMES-CERESIT-CE-40-VAGLEN---18/p/465494</t>
+          <t>https://praktiker.bg/bg/Lepila-za-plochki/LEPILO-ZA-PLOChKI-CERESIT-CM-17-SIV/p/435452</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2 kg, joints 1-8 mm</t>
+          <t>25 kg bag</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7666,7 +7662,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Price per 2 kg bag; charcoal to match Town Antracite.</t>
+          <t>Price per 25 kg bag. About 6 kg/m2 x 26 m2 with back-buttering for large format = 7 bags. Alt: Mapei Keraflex Maxi S1 Zero 19.49 EUR (p/130281).</t>
         </is>
       </c>
     </row>
@@ -7683,12 +7679,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Grout for wall (light grey), 2 kg</t>
+          <t>Grout for floor (charcoal), 2 kg</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ceresit CE 40 Манхатън (10) 2 kg</t>
+          <t>Ceresit CE 40 Въглен (18) 2 kg</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7703,7 +7699,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Fugi/FUGIRAShtA-SMES-CERESIT-CE-40-MANHATAN---10/p/432457</t>
+          <t>https://praktiker.bg/bg/Fugi/FUGIRAShtA-SMES-CERESIT-CE-40-VAGLEN---18/p/465494</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7713,7 +7709,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7728,7 +7724,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Price per 2 kg bag; light grey for wall tiles.</t>
+          <t>Price per 2 kg bag; charcoal to match Town Antracite.</t>
         </is>
       </c>
     </row>
@@ -7740,47 +7736,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pocket door kit</t>
+          <t>Grout</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pocket door cassette for drywall wall</t>
+          <t>Grout for wall (light grey), 2 kg</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JAP Profikit Standard 850 x 2100, UA/CW75</t>
+          <t>Ceresit CE 40 Манхатън (10) 2 kg</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>JAP</t>
+          <t>Ceresit</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>shop.baustoff-metall.bg</t>
+          <t>praktiker.bg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://shop.baustoff-metall.bg/product/3838/kaseta-za-plazgashta-vrata-850-h-2100-jap-profikit-standard-za-steni-ot-gipskarton-ua-cw75.html</t>
+          <t>https://praktiker.bg/bg/Fugi/FUGIRAShtA-SMES-CERESIT-CE-40-MANHATAN---10/p/432457</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>250.2</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>door 85 x 210 cm (clear opening 80 x 210), min wall 100 mm</t>
+          <t>2 kg, joints 1-8 mm</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7790,7 +7786,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Price incl. VAT (208.50 EUR ex VAT), in stock. Max leaf 60 kg / 40 mm thick. Eclisse Syntesis / Scrigno Essential / Krona Koblenz: no BG online price found - dealer quote needed. Knauf Pocket Kit Standard seen at polaris-bg.com about 497 EUR (not verified). Soft-close add-on: baustoff-metall product 3920.</t>
+          <t>Price per 2 kg bag; light grey for wall tiles.</t>
         </is>
       </c>
     </row>
@@ -7802,37 +7798,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Door leaf</t>
+          <t>Pocket door kit</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Paintable flush door leaf</t>
+          <t>Pocket door cassette for drywall wall</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Modulato primed door with frame 80x200x7 (art. 460545), leaf only used</t>
+          <t>JAP Profikit Standard 850 x 2100, UA/CW75</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Modulato</t>
+          <t>JAP</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>praktiker.bg</t>
+          <t>shop.baustoff-metall.bg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://praktiker.bg/bg/Vrati/GRUNDIRANA-VRATA-S-KASA-MODULATO-80H200H7-SM--DYaSNA/p/460545</t>
+          <t>https://shop.baustoff-metall.bg/product/3838/kaseta-za-plazgashta-vrata-850-h-2100-jap-profikit-standard-za-steni-ot-gipskarton-ua-cw75.html</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>109.99</t>
+          <t>250.2</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7842,7 +7838,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>80 x 200 cm</t>
+          <t>door 85 x 210 cm (clear opening 80 x 210), min wall 100 mm</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7852,7 +7848,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Closest stock primed flush leaf. An 82x205 leaf (and a matching kit) needs a custom leaf from a door maker - treat as custom/quote. Frame not needed for a pocket door.</t>
+          <t>Price incl. VAT (208.50 EUR ex VAT), in stock. Max leaf 60 kg / 40 mm thick. Eclisse Syntesis / Scrigno Essential / Krona Koblenz: no BG online price found - dealer quote needed. Knauf Pocket Kit Standard seen at polaris-bg.com about 497 EUR (not verified). Soft-close add-on: baustoff-metall product 3920.</t>
         </is>
       </c>
     </row>
@@ -7864,37 +7860,33 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pocket door lock</t>
+          <t>Door leaf</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pocket/sliding door lock with recessed pulls</t>
+          <t>Mirror door leaf, black aluminium frame</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>THIRARD sliding door lock, 50 mm backset, recessed handles with lock button</t>
+          <t>Custom aluminium-framed pocket door leaf 80x200, black anodised profile, 4 mm silver mirror both sides (safety film)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Thirard</t>
+          <t>local aluminium/glass workshop</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>emag.bg</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.emag.bg/brava-za-plyzgashta-se-vrata-thirard-50-mm-val-vdlybnati-dryzhki-s-buton-za-zakljuchvane-492073/pd/DRL09WBBM/</t>
-        </is>
-      </c>
+          <t>praktiker.bg</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7904,59 +7896,59 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>50 mm backset</t>
+          <t>80 x 200 cm</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>buy</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Seen in eMAG search results at 22.91 EUR, in stock; product page not fetched (eMAG blocking). Confirm matt black finish; if not black, get a black pocket-door lock from the kit dealer.</t>
+          <t>Replaces the paintable leaf. Fits the JAP Profikit cassette (row above); soft-close recommended. Doubles as the full-length hall mirror (LINDBYN removed).</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Bathroom</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AC outdoor</t>
+          <t>Pocket door lock</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Multi-split outdoor unit, 2 rooms, 5.3 kW</t>
+          <t>Pocket/sliding door lock with recessed pulls</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Gree GWHD(18)NK6LOO multi-split outdoor, R32</t>
+          <t>THIRARD sliding door lock, 50 mm backset, recessed handles with lock button</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Thirard</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>bittel.bg</t>
+          <t>emag.bg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.bittel.bg/vynshno-tjalo-na-multisplit-sistema-gree-gwhd-18-nk6-loo</t>
+          <t>https://www.emag.bg/brava-za-plyzgashta-se-vrata-thirard-50-mm-val-vdlybnati-dryzhki-s-buton-za-zakljuchvane-492073/pd/DRL09WBBM/</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7966,7 +7958,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>89.9 x 59.6 x 37.8 cm (W x H x D)</t>
+          <t>50 mm backset</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7976,7 +7968,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Bittel 906.00 EUR incl. VAT, in stock, delivery 15-30 days (verified on page). Other seller: respectclima.bg 906.00 EUR https://respectclima.bg/multisplit-gree-gwhd18nk6loo-lclh-klas-a (its spec says 55x74.5x30 cm, likely an error). Needs AC installer.</t>
+          <t>Seen in eMAG search results at 22.91 EUR, in stock; product page not fetched (eMAG blocking). Confirm matt black finish; if not black, get a black pocket-door lock from the kit dealer.</t>
         </is>
       </c>
     </row>
@@ -7988,17 +7980,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AC indoor</t>
+          <t>AC outdoor</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Multi-split indoor 9000 BTU, bedroom</t>
+          <t>Multi-split outdoor unit, 2 rooms, 5.3 kW</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Gree PULAR GWH09AGBXB/I (multi-split indoor)</t>
+          <t>Gree GWHD(18)NK6LOO multi-split outdoor, R32</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8008,17 +8000,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>respectclima.bg</t>
+          <t>bittel.bg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://respectclima.bg/vatreshno-tyalo-za-multi-split-gree-pular-gwh09agbxb-i-9-000-btu-klas-a</t>
+          <t>https://www.bittel.bg/vynshno-tjalo-na-multisplit-sistema-gree-gwhd-18-nk6-loo</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>222.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8028,7 +8020,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>77.9 x 26.0 x 18.5 cm</t>
+          <t>89.9 x 59.6 x 37.8 cm (W x H x D)</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8038,7 +8030,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>In stock, 2.6 kW cooling. Other seller: Bittel 222.00 EUR / 434.19 BGN (compatible-indoor table on https://www.bittel.bg/vynshno-tjalo-na-multisplit-sistema-gree-gwhd-18-nk6-loo). Sellers name it PULAR / PULAR II, not 'ECO II'; the /I multi code differs from the single-split GWH09AGB...-K6DNA set. Needs AC installer.</t>
+          <t>Bittel 906.00 EUR incl. VAT, in stock, delivery 15-30 days (verified on page). Other seller: respectclima.bg 906.00 EUR https://respectclima.bg/multisplit-gree-gwhd18nk6loo-lclh-klas-a (its spec says 55x74.5x30 cm, likely an error). Needs AC installer.</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8047,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Multi-split indoor 12000 BTU, living room</t>
+          <t>Multi-split indoor 9000 BTU, bedroom</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Gree PULAR II GWH12AGCXB-K6DNA1 (GWH12AGCXB/I) multi-split indoor</t>
+          <t>Gree PULAR GWH09AGBXB/I (multi-split indoor)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8070,17 +8062,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>x-clima.bg</t>
+          <t>respectclima.bg</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://x-clima.bg/product/gree-pular-ii-gwh12agcxb-k6dna1-multi-vatr-600001082384-365</t>
+          <t>https://respectclima.bg/vatreshno-tyalo-za-multi-split-gree-pular-gwh09agbxb-i-9-000-btu-klas-a</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>233.15</t>
+          <t>222.0</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8090,7 +8082,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>82.5 x 29.3 x 19.6 cm</t>
+          <t>77.9 x 26.0 x 18.5 cm</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8100,7 +8092,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>In stock, incl. VAT (was 245.42 EUR), 3.2 kW cooling. Other sellers: respectclima.bg 252.00 EUR https://respectclima.bg/vatreshno-tyalo-za-multi-split-gree-pular-gwh12agcxb-i-12-000-btu-klas-a ; Bittel 252.00 EUR / 492.87 BGN (outdoor page table). Listed as compatible with GWHD(18)NK6LOO. Needs AC installer.</t>
+          <t>In stock, 2.6 kW cooling. Other seller: Bittel 222.00 EUR / 434.19 BGN (compatible-indoor table on https://www.bittel.bg/vynshno-tjalo-na-multisplit-sistema-gree-gwhd-18-nk6-loo). Sellers name it PULAR / PULAR II, not 'ECO II'; the /I multi code differs from the single-split GWH09AGB...-K6DNA set. Needs AC installer.</t>
         </is>
       </c>
     </row>
@@ -8112,37 +8104,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AC installation</t>
+          <t>AC indoor</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Installation of multi-split: 1 outdoor + 2 indoor</t>
+          <t>Multi-split indoor 12000 BTU, living room</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Multi-split installation (quote needed)</t>
+          <t>Gree PULAR II GWH12AGCXB-K6DNA1 (GWH12AGCXB/I) multi-split indoor</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>bittel.bg</t>
+          <t>x-clima.bg</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.bittel.bg/terms/montaj-na-klimatici</t>
+          <t>https://x-clima.bg/product/gree-pular-ii-gwh12agcxb-k6dna1-multi-vatr-600001082384-365</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>233.15</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8152,7 +8144,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>82.5 x 29.3 x 19.6 cm</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8162,59 +8154,59 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No BG seller found listing a multi-split installation price. Bittel lists only single-split standard installation from 163.61 EUR ex VAT per 9-14k BTU unit (about 196 EUR incl. VAT), so expect roughly 400 EUR or more for 2 indoor units plus any extra piping. respectclima says its indoor prices include installation up to 3 m of pipe but also that installation is quoted after a site visit. Get a quote.</t>
+          <t>In stock, incl. VAT (was 245.42 EUR), 3.2 kW cooling. Other sellers: respectclima.bg 252.00 EUR https://respectclima.bg/vatreshno-tyalo-za-multi-split-gree-pular-gwh12agcxb-i-12-000-btu-klas-a ; Bittel 252.00 EUR / 492.87 BGN (outdoor page table). Listed as compatible with GWHD(18)NK6LOO. Needs AC installer.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lighting</t>
+          <t>AC installation</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Recessed downlight fitting, black (living, 2700K line)</t>
+          <t>Installation of multi-split: 1 outdoor + 2 indoor</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Lightex recessed GU10 fitting O90 mm black, 304AC0110020</t>
+          <t>Multi-split installation (quote needed)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lightex</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>eMAG (emag.bg)</t>
+          <t>bittel.bg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/luna-za-vgrazhdane-lightex-gu10-f90mm-75mm-cheren-304ac0110020/pd/D5T2CSYBM/</t>
+          <t>https://www.bittel.bg/terms/montaj-na-klimatici</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>outer O9 cm, cut-out O7.5 cm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8224,7 +8216,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>fitting only, needs GU10 lamp (24b); fixed, black trim. price_bgn = EUR x 1.95583 (shops show EUR only)</t>
+          <t>No BG seller found listing a multi-split installation price. Bittel lists only single-split standard installation from 163.61 EUR ex VAT per 9-14k BTU unit (about 196 EUR incl. VAT), so expect roughly 400 EUR or more for 2 indoor units plus any extra piping. respectclima says its indoor prices include installation up to 3 m of pipe but also that installation is quoted after a site visit. Get a quote.</t>
         </is>
       </c>
     </row>
@@ -8241,17 +8233,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>GU10 LED lamp 2700K CRI90 dimmable</t>
+          <t>Recessed downlight fitting, black (living, 2700K line)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Philips GU10 LED 6.2W 575lm CRI90 WarmGlow 2200-2700K dim, EAN 8718699774097</t>
+          <t>Lightex recessed GU10 fitting O90 mm black, 304AC0110020</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Lightex</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8261,12 +8253,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/philips-gu10-led-6-2w-575lm-cri90-2200-2700k-warmglow-dim-vmesto-80w-krushka-8718699774097/pd/DZ8CJHMBM/</t>
+          <t>https://www.emag.bg/luna-za-vgrazhdane-lightex-gu10-f90mm-75mm-cheren-304ac0110020/pd/D5T2CSYBM/</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8276,7 +8268,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>GU10 O5 cm</t>
+          <t>outer O9 cm, cut-out O7.5 cm</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8286,14 +8278,14 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>dimmable (trailing-edge LED dimmer). GU10 lamp+fitting chosen because integrated CRI90 D80 units (Ledvance Spot Adjust LED799622 / Darklight IP44 LED799806) cost 82.99 EUR each</t>
+          <t>fitting only, needs GU10 lamp (24b); fixed, black trim. price_bgn = EUR x 1.95583 (shops show EUR only)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8303,17 +8295,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Recessed downlight fitting, black (kitchen, 3000K line)</t>
+          <t>GU10 LED lamp 2700K CRI90 dimmable</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Lightex recessed GU10 fitting O90 mm black, 304AC0110020</t>
+          <t>Philips GU10 LED 6.2W 575lm CRI90 WarmGlow 2200-2700K dim, EAN 8718699774097</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lightex</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8323,22 +8315,22 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/luna-za-vgrazhdane-lightex-gu10-f90mm-75mm-cheren-304ac0110020/pd/D5T2CSYBM/</t>
+          <t>https://www.emag.bg/philips-gu10-led-6-2w-575lm-cri90-2200-2700k-warmglow-dim-vmesto-80w-krushka-8718699774097/pd/DZ8CJHMBM/</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>18.11</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>outer O9 cm, cut-out O7.5 cm</t>
+          <t>GU10 O5 cm</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8348,14 +8340,14 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>fitting only, lamp in 24d</t>
+          <t>dimmable (trailing-edge LED dimmer). GU10 lamp+fitting chosen because integrated CRI90 D80 units (Ledvance Spot Adjust LED799622 / Darklight IP44 LED799806) cost 82.99 EUR each</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kitchen/Bath</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8365,17 +8357,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GU10 LED lamp 3000K CRI90 dimmable (5 kitchen + 4 bath)</t>
+          <t>Recessed downlight fitting, black (kitchen, 3000K line)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ledvance PAR16 GU10 6.1W 575lm 3000K 36deg CRI90 dimmable, code 8845173547817</t>
+          <t>Lightex recessed GU10 fitting O90 mm black, 304AC0110020</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ledvance</t>
+          <t>Lightex</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8385,22 +8377,22 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/led-krushka-par16-gu10-ledvance-6-1w-ekv-80w-575-lm-3000k-36-cri-90-dimiruema-prozrachno-styklo-kod-8845173547817/pd/DR4G582BM/</t>
+          <t>https://www.emag.bg/luna-za-vgrazhdane-lightex-gu10-f90mm-75mm-cheren-304ac0110020/pd/D5T2CSYBM/</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>GU10 O5 cm</t>
+          <t>outer O9 cm, cut-out O7.5 cm</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8410,14 +8402,14 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>marketplace seller SPGROUP; lamps for 24c, 24e, 24f</t>
+          <t>fitting only, lamp in 24d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Kitchen/Bath</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8427,17 +8419,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Recessed downlight for IP44 zone (bath ceiling), black</t>
+          <t>GU10 LED lamp 3000K CRI90 dimmable (5 kitchen + 4 bath)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Maytoni DL032-2-01B recessed GU10 IP65 black</t>
+          <t>Ledvance PAR16 GU10 6.1W 575lm 3000K 36deg CRI90 dimmable, code 8845173547817</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Maytoni</t>
+          <t>Ledvance</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8447,22 +8439,22 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/prozhektor-maytoni-za-vgrazhdane-v-tavan-1xgu10-50w-max-cheren-8-5x4-5-sm-ip65-dl032-2-01b/pd/DHRBGWYBM/</t>
+          <t>https://www.emag.bg/led-krushka-par16-gu10-ledvance-6-1w-ekv-80w-575-lm-3000k-36-cri-90-dimiruema-prozrachno-styklo-kod-8845173547817/pd/DR4G582BM/</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>O8.5 cm x h4.5 cm; cut-out not stated</t>
+          <t>GU10 O5 cm</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8472,14 +8464,14 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>no IP44 GU10 fitting with ~8 cm cut-out found; same IP65 model for all 4 bath units so trims match; lamp from 24d</t>
+          <t>marketplace seller SPGROUP; lamps for 24c, 24e, 24f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bath (shower)</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8489,7 +8481,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Recessed downlight IP65 over shower, black</t>
+          <t>Recessed downlight for IP44 zone (bath ceiling), black</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8519,7 +8511,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8534,14 +8526,14 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>lamp from 24d; electrician to confirm bathroom zone rules</t>
+          <t>no IP44 GU10 fitting with ~8 cm cut-out found; same IP65 model for all 4 bath units so trims match; lamp from 24d</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Living (shelves/cove)</t>
+          <t>Bath (shower)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8551,17 +8543,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LED strip 24V 2700K CRI90, 5 m roll</t>
+          <t>Recessed downlight IP65 over shower, black</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>COB LED strip 24V 15W/m 512LED/m 1650lm/m CRI90 2700K IP20, SP512D15W 27K</t>
+          <t>Maytoni DL032-2-01B recessed GU10 IP65 black</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>unbranded (SP512D15W)</t>
+          <t>Maytoni</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8571,22 +8563,22 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/cob-led-lenta-24v-5-metra-15w-m-75w-512led-m-1650lm-m-cri90-visok-glanc-ip20-neprekysnata-svetlina-toplo-bjalo-2700k-sp512d15w-91692-27k/pd/D3WXZXYBM/</t>
+          <t>https://www.emag.bg/prozhektor-maytoni-za-vgrazhdane-v-tavan-1xgu10-50w-max-cheren-8-5x4-5-sm-ip65-dl032-2-01b/pd/DHRBGWYBM/</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>5 m roll</t>
+          <t>O8.5 cm x h4.5 cm; cut-out not stated</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8596,7 +8588,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>price per 5 m roll, seen in eMAG search listing (product page fetch was rate-limited); COB = no dots in profile</t>
+          <t>lamp from 24d; electrician to confirm bathroom zone rules</t>
         </is>
       </c>
     </row>
@@ -8613,42 +8605,42 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Aluminium profile 2 m kit for LED strip</t>
+          <t>LED strip 24V 2700K CRI90, 5 m roll</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Vivalux PROFILE S 2M KIT, VIV003754</t>
+          <t>COB LED strip 24V 15W/m 512LED/m 1650lm/m CRI90 2700K IP20, SP512D15W 27K</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vivalux</t>
+          <t>unbranded (SP512D15W)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vivalux (vivalux.bg)</t>
+          <t>eMAG (emag.bg)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://vivalux.bg/bg/product/viv003754</t>
+          <t>https://www.emag.bg/cob-led-lenta-24v-5-metra-15w-m-75w-512led-m-1650lm-m-cri90-visok-glanc-ip20-neprekysnata-svetlina-toplo-bjalo-2700k-sp512d15w-91692-27k/pd/D3WXZXYBM/</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>200 x 1.59 x 0.6 cm</t>
+          <t>5 m roll</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8658,7 +8650,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>price per 2 m kit; 5 kits = 10 m; check diffuser and strip width fit</t>
+          <t>price per 5 m roll, seen in eMAG search listing (product page fetch was rate-limited); COB = no dots in profile</t>
         </is>
       </c>
     </row>
@@ -8675,12 +8667,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>24V LED driver 120W</t>
+          <t>Aluminium profile 2 m kit for LED strip</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Vivalux PSD LED driver 120W, 240V in / 24VDC out, IP20, VIV004693</t>
+          <t>Vivalux PROFILE S 2M KIT, VIV003754</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8695,22 +8687,22 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://vivalux.bg/bg/product/viv004693</t>
+          <t>https://vivalux.bg/bg/product/viv003754</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>18.8 x 4.6 x 3.5 cm</t>
+          <t>200 x 1.59 x 0.6 cm</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8720,59 +8712,59 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>needs electrician; stock not stated on page; non-dimmable - pick a dimmable driver if dimming wanted</t>
+          <t>price per 2 m kit; 5 kits = 10 m; check diffuser and strip width fit</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Whole apartment</t>
+          <t>Living (shelves/cove)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Double socket 2P+E white, child shutters (frame incl.)</t>
+          <t>24V LED driver 120W</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design SDD311221 double socket white</t>
+          <t>Vivalux PSD LED driver 120W, 240V in / 24VDC out, IP20, VIV004693</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Vivalux</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>eMAG (emag.bg)</t>
+          <t>Vivalux (vivalux.bg)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/kontakt-schneider-sedna-design-sdd311221-dvoen-2p-e-sys-zashtita-za-deca-bjal-sch-sdd311221/pd/DMGF9MYBM/</t>
+          <t>https://vivalux.bg/bg/product/viv004693</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>approx 7.3 x 14.4 cm double unit</t>
+          <t>18.8 x 4.6 x 3.5 cm</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8782,14 +8774,14 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Sedna Design units come with frame; 2-gang flush box at 71 mm spacing</t>
+          <t>needs electrician; stock not stated on page; non-dimmable - pick a dimmable driver if dimming wanted</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Whole apartment</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8799,12 +8791,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Double socket 2P+E anthracite/black (kitchen)</t>
+          <t>Double socket 2P+E white, child shutters (frame incl.)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design SDD314221 double socket anthracite</t>
+          <t>Schneider Sedna Design SDD311221 double socket white</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8819,22 +8811,22 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/kontakt-schneider-sedna-design-sdd314221-dvoen-2p-e-sys-zashtita-za-deca-antracit-sch-sdd314221/pd/DJGF9MYBM/</t>
+          <t>https://www.emag.bg/kontakt-schneider-sedna-design-sdd311221-dvoen-2p-e-sys-zashtita-za-deca-bjal-sch-sdd311221/pd/DMGF9MYBM/</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>approx 7.3 x 14.4 cm</t>
+          <t>approx 7.3 x 14.4 cm double unit</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8844,14 +8836,14 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>complete unit incl. frame</t>
+          <t>Sedna Design units come with frame; 2-gang flush box at 71 mm spacing</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Whole apartment</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8861,12 +8853,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Switch one-way white</t>
+          <t>Double socket 2P+E anthracite/black (kitchen)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design SDD111101 one-way switch white</t>
+          <t>Schneider Sedna Design SDD314221 double socket anthracite</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8881,22 +8873,22 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/prevkljuchvatel-schneider-sedna-design-sdd111101-bjal-sch-sdd111101-mp/pd/D2GF9MYBM/</t>
+          <t>https://www.emag.bg/kontakt-schneider-sedna-design-sdd314221-dvoen-2p-e-sys-zashtita-za-deca-antracit-sch-sdd314221/pd/DJGF9MYBM/</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>7.3 x 7.3 cm</t>
+          <t>approx 7.3 x 14.4 cm</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8906,7 +8898,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>incl. frame; 7 of the 11 one-way/2-way</t>
+          <t>complete unit incl. frame</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8915,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Switch 2-way (staircase) white</t>
+          <t>Switch one-way white</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design staircase switch 16A white, EAN 3606481478337</t>
+          <t>Schneider Sedna Design SDD111101 one-way switch white</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8943,17 +8935,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/schneider-sedna-design-kljuch-stylbishten-16a-bjal-3606481478337/pd/DGFWJR3BM/</t>
+          <t>https://www.emag.bg/prevkljuchvatel-schneider-sedna-design-sdd111101-bjal-sch-sdd111101-mp/pd/D2GF9MYBM/</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>36.03</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8968,7 +8960,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>price high (marketplace seller); white SDD111106 not found cheaper on eMAG - check electrical wholesalers</t>
+          <t>incl. frame; 7 of the 11 one-way/2-way</t>
         </is>
       </c>
     </row>
@@ -8985,12 +8977,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cross (intermediate) switch white</t>
+          <t>Switch 2-way (staircase) white</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design cross switch white, EAN 3606481478139</t>
+          <t>Schneider Sedna Design staircase switch 16A white, EAN 3606481478337</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9005,17 +8997,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/krystosan-prevkljuchvatel-schneider-sedna-design-bjal-hh3606481478139/pd/DP92QJYBM/</t>
+          <t>https://www.emag.bg/schneider-sedna-design-kljuch-stylbishten-16a-bjal-3606481478337/pd/DGFWJR3BM/</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>36.03</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9030,7 +9022,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>used between two 2-way switches</t>
+          <t>price high (marketplace seller); white SDD111106 not found cheaper on eMAG - check electrical wholesalers</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9039,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Double (2-gang) switch white</t>
+          <t>Cross (intermediate) switch white</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design double switch white with indicator light, EAN 5944451373472</t>
+          <t>Schneider Sedna Design cross switch white, EAN 3606481478139</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9067,12 +9059,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/dvoen-prevkljuchvatel-schneider-sedna-design-sys-svetlina-bjal-5944451373472/pd/DBJ2QJYBM/</t>
+          <t>https://www.emag.bg/krystosan-prevkljuchvatel-schneider-sedna-design-bjal-hh3606481478139/pd/DP92QJYBM/</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9090,12 +9082,16 @@
           <t>buy</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>used between two 2-way switches</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bath/Balcony</t>
+          <t>Whole apartment</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9105,12 +9101,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Socket IP44 with lid, white</t>
+          <t>Double (2-gang) switch white</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Schneider New Sedna SDD211024 2P+E IP44 white with lid</t>
+          <t>Schneider Sedna Design double switch white with indicator light, EAN 5944451373472</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9125,22 +9121,22 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/kontakt-schneider-new-sedna-2p-f-s-predpazna-kapachka-s-kapak-za-kran-pruzhinna-vryzka-ip44-bjal-sdd211024/pd/D8KX1RYBM/</t>
+          <t>https://www.emag.bg/dvoen-prevkljuchvatel-schneider-sedna-design-sys-svetlina-bjal-5944451373472/pd/DBJ2QJYBM/</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>approx 7.3 x 7.3 cm</t>
+          <t>7.3 x 7.3 cm</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9148,16 +9144,12 @@
           <t>buy</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>bathroom zone 2+ only; on RCD</t>
-        </is>
-      </c>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Living/Office</t>
+          <t>Bath/Balcony</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9167,12 +9159,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Data socket RJ45 (double) white</t>
+          <t>Socket IP44 with lid, white</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design SDD111452 double RJ45 Cat5e white</t>
+          <t>Schneider New Sedna SDD211024 2P+E IP44 white with lid</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9187,22 +9179,22 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/dvoen-internet-kontakt-rj45-5e-ip20-bjal-schneider-sedna-design-sdd111452/pd/DLM9CH3BM/</t>
+          <t>https://www.emag.bg/kontakt-schneider-new-sedna-2p-f-s-predpazna-kapachka-s-kapak-za-kran-pruzhinna-vryzka-ip44-bjal-sdd211024/pd/D8KX1RYBM/</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>7.3 x 7.3 cm</t>
+          <t>approx 7.3 x 7.3 cm</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9210,12 +9202,16 @@
           <t>buy</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>bathroom zone 2+ only; on RCD</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Living</t>
+          <t>Living/Office</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9225,12 +9221,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TV socket white</t>
+          <t>Data socket RJ45 (double) white</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Schneider Sedna Design SDD111471 TV end socket 4dB white</t>
+          <t>Schneider Sedna Design SDD111452 double RJ45 Cat5e white</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9245,17 +9241,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/bjala-tv-rozetka-sedna-design-schneider-vnssdd111471/pd/DG2CWVYBM/</t>
+          <t>https://www.emag.bg/dvoen-internet-kontakt-rj45-5e-ip20-bjal-schneider-sedna-design-sdd111452/pd/DLM9CH3BM/</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9273,7 +9269,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9283,12 +9279,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Consumer board 24 modules, flush</t>
+          <t>TV socket white</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Schneider Easy9 EU EZ9EUB212 flush board 2x12 modules, PE+N bars, solid door</t>
+          <t>Schneider Sedna Design SDD111471 TV end socket 4dB white</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9303,12 +9299,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/schneider-easy9-eu-malko-razpredelitelno-tablo-24-modula-s-pe-n-shina-pylna-vrata-vgradeno-24ke-ez9eub212/pd/DM8SF5YBM/</t>
+          <t>https://www.emag.bg/bjala-tv-rozetka-sedna-design-schneider-vnssdd111471/pd/DG2CWVYBM/</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>9.93</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9318,7 +9314,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>24 modules (2 x 12)</t>
+          <t>7.3 x 7.3 cm</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9326,16 +9322,12 @@
           <t>buy</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>needs electrician</t>
-        </is>
-      </c>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hallway (board)</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9345,17 +9337,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MCB 1P B16</t>
+          <t>Consumer board 24 modules, flush</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ABB 1P B16 4.5kA, 2CDS241001R0165</t>
+          <t>Schneider Easy9 EU EZ9EUB212 flush board 2x12 modules, PE+N bars, solid door</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9365,22 +9357,22 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/avtomatichen-elektricheski-predpazitel-abb-shirina-1-modul-4-5ka-1p-harakteristika-b-16a-2cds241001r0165/pd/DBF39HYBM/</t>
+          <t>https://www.emag.bg/schneider-easy9-eu-malko-razpredelitelno-tablo-24-modula-s-pe-n-shina-pylna-vrata-vgradeno-24ke-ez9eub212/pd/DM8SF5YBM/</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>34.93</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>1 module</t>
+          <t>24 modules (2 x 12)</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9390,7 +9382,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>socket circuits; electrician finalises schedule</t>
+          <t>needs electrician</t>
         </is>
       </c>
     </row>
@@ -9407,17 +9399,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MCB 1P B10</t>
+          <t>MCB 1P B16</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Schneider Acti9 iC60N 1P B10, A9F03110</t>
+          <t>ABB 1P B16 4.5kA, 2CDS241001R0165</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9427,17 +9419,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/avtomatichen-prekysvach-1p-b10a-ic60n-schneider-a9f03110-008925/pd/D686X5MBM/</t>
+          <t>https://www.emag.bg/avtomatichen-elektricheski-predpazitel-abb-shirina-1-modul-4-5ka-1p-harakteristika-b-16a-2cds241001r0165/pd/DBF39HYBM/</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9452,7 +9444,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>lighting circuits</t>
+          <t>socket circuits; electrician finalises schedule</t>
         </is>
       </c>
     </row>
@@ -9469,12 +9461,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MCB 1P C20</t>
+          <t>MCB 1P B10</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Schneider Resi9 1P C20 6kA, A9K24120</t>
+          <t>Schneider Acti9 iC60N 1P B10, A9F03110</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9489,17 +9481,17 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/avtomatichen-elektricheski-predpazitel-schneider-1p-6000a-kriva-na-izkljuchvane-c-20-a-a9k24120/pd/DBSS39YBM/</t>
+          <t>https://www.emag.bg/avtomatichen-prekysvach-1p-b10a-ic60n-schneider-a9f03110-008925/pd/D686X5MBM/</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9514,7 +9506,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>oven/washer; an induction hob may need 32A or 3-phase - electrician</t>
+          <t>lighting circuits</t>
         </is>
       </c>
     </row>
@@ -9531,17 +9523,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RCD 2P 40A 30mA type A</t>
+          <t>MCB 1P C20</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Hager CD240J RCCB 2P 40A 30mA type A</t>
+          <t>Schneider Resi9 1P C20 6kA, A9K24120</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hager</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9551,22 +9543,22 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/diferencialen-prekysvach-rccb-2p-40a-30ma-tip-a-cd240j-hager-1123715/pd/DRNCW2MBM/</t>
+          <t>https://www.emag.bg/avtomatichen-elektricheski-predpazitel-schneider-1p-6000a-kriva-na-izkljuchvane-c-20-a-a9k24120/pd/DBSS39YBM/</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2 modules</t>
+          <t>1 module</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9576,14 +9568,14 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>type A chosen; cheaper type AC: ABB FH202AC-40/0.03 at 33.20 EUR</t>
+          <t>oven/washer; an induction hob may need 32A or 3-phase - electrician</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Hallway (board)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9593,17 +9585,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Smoke alarm, 10-year sealed battery</t>
+          <t>RCD 2P 40A 30mA type A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>FireAngel FA6120-INT optical smoke alarm</t>
+          <t>Hager CD240J RCCB 2P 40A 30mA type A</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FireAngel</t>
+          <t>Hager</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9613,22 +9605,22 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/detektor-za-dim-fireangel-fa6120-samostojatelen-novo-pokolenie-optichen-senzor-zapechatana-baterija-za-10-godini-fa-6120-int/pd/DQ6VL1MBM/</t>
+          <t>https://www.emag.bg/diferencialen-prekysvach-rccb-2p-40a-30ma-tip-a-cd240j-hager-1123715/pd/DRNCW2MBM/</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>approx O11.8 x 3.1 cm</t>
+          <t>2 modules</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9636,7 +9628,11 @@
           <t>buy</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>type A chosen; cheaper type AC: ABB FH202AC-40/0.03 at 33.20 EUR</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9651,17 +9647,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Video intercom handset (apartment unit)</t>
+          <t>Smoke alarm, 10-year sealed battery</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ACO INS-MPR 4 colour 4in video intercom with handset</t>
+          <t>FireAngel FA6120-INT optical smoke alarm</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ACO</t>
+          <t>FireAngel</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9671,12 +9667,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/videodomofon-aco-ins-mpr-4-cveten-ekran-4-lcd-tft-sys-slushalka-s-funkcija-za-otvarjane-na-porta-bjal-1-br-5908066703246/pd/DXYCFK2BM/</t>
+          <t>https://www.emag.bg/detektor-za-dim-fireangel-fa6120-samostojatelen-novo-pokolenie-optichen-senzor-zapechatana-baterija-za-10-godini-fa-6120-int/pd/DQ6VL1MBM/</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>407.24</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9686,7 +9682,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>wall unit</t>
+          <t>approx O11.8 x 3.1 cm</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9694,11 +9690,7 @@
           <t>buy</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>placeholder price; buy the monitor matching the block's system (Commax/Urmet/etc.) via the building's installer</t>
-        </is>
-      </c>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9713,17 +9705,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Doorbell, wired 230V</t>
+          <t>Video intercom handset (apartment unit)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Wired doorbell white 220V (unbranded), 15 x 9.5 x 4.5 cm</t>
+          <t>ACO INS-MPR 4 colour 4in video intercom with handset</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>unbranded</t>
+          <t>ACO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9733,12 +9725,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.emag.bg/kabelen-zvynec-za-vrata-bjal-15x9-5x4-5sm-220v-p8bu89zvpjkx/pd/DMRYFL2BM/</t>
+          <t>https://www.emag.bg/videodomofon-aco-ins-mpr-4-cveten-ekran-4-lcd-tft-sys-slushalka-s-funkcija-za-otvarjane-na-porta-bjal-1-br-5908066703246/pd/DXYCFK2BM/</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>25.68</t>
+          <t>407.24</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9748,7 +9740,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>15 x 9.5 x 4.5 cm</t>
+          <t>wall unit</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9758,59 +9750,59 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>bell push not included; skip if the intercom handles the door call</t>
+          <t>placeholder price; buy the monitor matching the block's system (Commax/Urmet/etc.) via the building's installer</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Whole apartment</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SPC click vinyl, oak, integrated IXPE underlay</t>
+          <t>Doorbell, wired 230V</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Vinyl SPC Oak Hope 1220x228x5+1 mm, art. 60906342</t>
+          <t>Wired doorbell white 220V (unbranded), 15 x 9.5 x 4.5 cm</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>BAUHAUS (brand not stated)</t>
+          <t>unbranded</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>BAUHAUS (bauhaus.bg)</t>
+          <t>eMAG (emag.bg)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://bauhaus.bg/vinil-spc-dab-hope/p/173677</t>
+          <t>https://www.emag.bg/kabelen-zvynec-za-vrata-bjal-15x9-5x4-5sm-220v-p8bu89zvpjkx/pd/DMRYFL2BM/</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>25.68</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>122 x 22.8 cm plank, 0.6 cm total; 1.94705 m2/pack</t>
+          <t>15 x 9.5 x 4.5 cm</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9820,7 +9812,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>price per pack (24.95 EUR/m2); 26 packs = 50.6 m2 for 49.5 m2 need; 100% waterproof; underlay integrated so no separate underlay line; 40 packs in stock. No BG listing found that states &gt;=0.55 mm wear layer (Praktiker/Bauhaus pages omit it). Lighter alt: Praktiker Kronostep Oak Orchidea 19.99 EUR/m2, class 32, no integrated underlay</t>
+          <t>bell push not included; skip if the intercom handles the door call</t>
         </is>
       </c>
     </row>
@@ -9837,50 +9829,112 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
+          <t>SPC click vinyl, oak, integrated IXPE underlay</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Vinyl SPC Oak Hope 1220x228x5+1 mm, art. 60906342</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BAUHAUS (brand not stated)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>BAUHAUS (bauhaus.bg)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://bauhaus.bg/vinil-spc-dab-hope/p/173677</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>48.58</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>122 x 22.8 cm plank, 0.6 cm total; 1.94705 m2/pack</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>price per pack (24.95 EUR/m2); 26 packs = 50.6 m2 for 49.5 m2 need; 100% waterproof; underlay integrated so no separate underlay line; 40 packs in stock. No BG listing found that states &gt;=0.55 mm wear layer (Praktiker/Bauhaus pages omit it). Lighter alt: Praktiker Kronostep Oak Orchidea 19.99 EUR/m2, class 32, no integrated underlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Whole apartment</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
           <t>Skirting board white PVC 80 mm</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>Vilo Sempla 80 701 white PVC skirting, 2.4 m</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>Vilo</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Praktiker (praktiker.bg)</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>https://praktiker.bg/bg/Pervazi-za-laminat/PODOV-PVC-PERVAZ-VILO-SEMPLA-80-701-BYaL/p/233072</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>8.49</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="J154" t="inlineStr">
         <is>
           <t>240 x 8 cm</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
         <is>
           <t>price per piece; corners/end caps not listed, buy as needed</t>
         </is>
